--- a/mixs-templates/Mims_plus_combinations/MimsSoil.xlsx
+++ b/mixs-templates/Mims_plus_combinations/MimsSoil.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS1"/>
+  <dimension ref="A1:CT1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,9 +902,14 @@
           <t>misc_param</t>
         </is>
       </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"aerobe,anaerobe,facultative,microaerophilic,microanaerobe,obligate aerobe,obligate anaerobe"</formula1>
     </dataValidation>
@@ -929,6 +934,9 @@
     <dataValidation sqref="CB2:CB1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"excessively drained,moderately well,poorly,somewhat poorly,very poorly,well"</formula1>
     </dataValidation>
+    <dataValidation sqref="CT2:CT1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"autumn [NCIT:C94733],spring [NCIT:C94731],summer [NCIT:C94732],winter [NCIT:C94730]"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
